--- a/docs/design/ACSMS-SCR-006/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_支店マスタ明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-006/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_支店マスタ明細検索画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1512,22 +1512,88 @@
       <c r="AF2" s="10" t="n"/>
       <c r="AG2" s="11" t="n"/>
     </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Dao Van Thang</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <t>画面設計書 v1.3 対応：検索条件4項目を追加（shiten_code, kanri_shiten_id, jastem_toriatsukai_tenpo_code, kinyu_shiten_flg）。リクエストパラメータ表＋§4.3 / §4.4 / §4.5 SQLを更新</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="H1:J1"/>
+  <mergeCells count="21">
     <mergeCell ref="R1:V1"/>
-    <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="R2:V2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="W3:AA3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="R2:V2"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1700,7 +1766,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2126,7 +2192,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2941,7 +3007,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3215,7 +3281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK117"/>
+  <dimension ref="A1:AK129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3376,7 +3442,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3669,7 +3735,7 @@
       <c r="AJ11" s="10" t="n"/>
       <c r="AK11" s="11" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="36" customHeight="1">
       <c r="B12" s="33" t="inlineStr">
         <is>
           <t>リクエストパラメーター</t>
@@ -3684,7 +3750,7 @@
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>?shiten_name={shiten_name}&amp;page={page}&amp;per_page={per_page}&amp;sort_by={sort_by}&amp;sort_order={sort_order}</t>
+          <t>クエリパラメータ（shiten_code, shiten_name, kanri_shiten_id, jastem_toriatsukai_tenpo_code, kinyu_shiten_flg, page, per_page, sort_by, sort_order）</t>
         </is>
       </c>
       <c r="K12" s="10" t="n"/>
@@ -4052,7 +4118,7 @@
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>shiten_name</t>
+          <t>shiten_code</t>
         </is>
       </c>
       <c r="D23" s="10" t="n"/>
@@ -4093,13 +4159,13 @@
       <c r="AA23" s="10" t="n"/>
       <c r="AB23" s="11" t="n"/>
       <c r="AC23" s="17" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="AD23" s="10" t="n"/>
       <c r="AE23" s="11" t="n"/>
       <c r="AF23" s="19" t="inlineStr">
         <is>
-          <t>支店名（部分一致検索）</t>
+          <t>支店コード（部分一致検索）</t>
         </is>
       </c>
       <c r="AG23" s="10" t="n"/>
@@ -4114,7 +4180,7 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>shiten_name</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -4128,7 +4194,7 @@
       <c r="L24" s="11" t="n"/>
       <c r="M24" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N24" s="10" t="n"/>
@@ -4154,12 +4220,14 @@
       <c r="Z24" s="10" t="n"/>
       <c r="AA24" s="10" t="n"/>
       <c r="AB24" s="11" t="n"/>
-      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AC24" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AD24" s="10" t="n"/>
       <c r="AE24" s="11" t="n"/>
       <c r="AF24" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（デフォルト: 1）</t>
+          <t>支店名（部分一致検索）</t>
         </is>
       </c>
       <c r="AG24" s="10" t="n"/>
@@ -4168,13 +4236,13 @@
       <c r="AJ24" s="10" t="n"/>
       <c r="AK24" s="11" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="B25" s="31" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -4219,7 +4287,7 @@
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数（デフォルト: 20、最大: 100）</t>
+          <t>管理支店ID（完全一致検索）。プルダウンは ACSMS-API-COMMON-004 を参照</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -4228,13 +4296,13 @@
       <c r="AJ25" s="10" t="n"/>
       <c r="AK25" s="11" t="n"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="18" customHeight="1">
       <c r="B26" s="31" t="n">
         <v>4</v>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>jastem_toriatsukai_tenpo_code</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -4274,12 +4342,14 @@
       <c r="Z26" s="10" t="n"/>
       <c r="AA26" s="10" t="n"/>
       <c r="AB26" s="11" t="n"/>
-      <c r="AC26" s="17" t="inlineStr"/>
+      <c r="AC26" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="AD26" s="10" t="n"/>
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>ソート項目（shiten_code, shiten_name, kanri_shiten_name。デフォルト: shiten_code）</t>
+          <t>JASTEM_データ送信取扱店舗コード（部分一致検索）</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -4288,13 +4358,13 @@
       <c r="AJ26" s="10" t="n"/>
       <c r="AK26" s="11" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1">
+    <row r="27" ht="36" customHeight="1">
       <c r="B27" s="31" t="n">
         <v>5</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>kinyu_shiten_flg</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -4308,7 +4378,7 @@
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N27" s="10" t="n"/>
@@ -4339,7 +4409,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>ソート方向（asc / desc。デフォルト: asc）</t>
+          <t>金融機関支店フラグ（true=金融機関支店, false=金融機関支店以外, 未指定=全選択 — 絞り込みなし）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -4348,24 +4418,193 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="19.5" customHeight="1"/>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1"/>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>項目ID</t>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="10" t="n"/>
+      <c r="K28" s="10" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="n"/>
+      <c r="O28" s="10" t="n"/>
+      <c r="P28" s="11" t="n"/>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" s="10" t="n"/>
+      <c r="S28" s="11" t="n"/>
+      <c r="T28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U28" s="10" t="n"/>
+      <c r="V28" s="10" t="n"/>
+      <c r="W28" s="10" t="n"/>
+      <c r="X28" s="11" t="n"/>
+      <c r="Y28" s="17" t="inlineStr"/>
+      <c r="Z28" s="10" t="n"/>
+      <c r="AA28" s="10" t="n"/>
+      <c r="AB28" s="11" t="n"/>
+      <c r="AC28" s="17" t="inlineStr"/>
+      <c r="AD28" s="10" t="n"/>
+      <c r="AE28" s="11" t="n"/>
+      <c r="AF28" s="19" t="inlineStr">
+        <is>
+          <t>ページ番号（デフォルト: 1）</t>
+        </is>
+      </c>
+      <c r="AG28" s="10" t="n"/>
+      <c r="AH28" s="10" t="n"/>
+      <c r="AI28" s="10" t="n"/>
+      <c r="AJ28" s="10" t="n"/>
+      <c r="AK28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="11" t="n"/>
+      <c r="Y29" s="17" t="inlineStr"/>
+      <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="11" t="n"/>
+      <c r="AC29" s="17" t="inlineStr"/>
+      <c r="AD29" s="10" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（デフォルト: 20、最大: 100）</t>
+        </is>
+      </c>
+      <c r="AG29" s="10" t="n"/>
+      <c r="AH29" s="10" t="n"/>
+      <c r="AI29" s="10" t="n"/>
+      <c r="AJ29" s="10" t="n"/>
+      <c r="AK29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="B30" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>sort_by</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="11" t="n"/>
+      <c r="Y30" s="17" t="inlineStr"/>
+      <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="11" t="n"/>
+      <c r="AC30" s="17" t="inlineStr"/>
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="19" t="inlineStr">
+        <is>
+          <t>ソート項目（shiten_code, shiten_name, kanri_shiten_name, updated_at。デフォルト: updated_at）</t>
+        </is>
+      </c>
+      <c r="AG30" s="10" t="n"/>
+      <c r="AH30" s="10" t="n"/>
+      <c r="AI30" s="10" t="n"/>
+      <c r="AJ30" s="10" t="n"/>
+      <c r="AK30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -4377,44 +4616,40 @@
       <c r="J31" s="10" t="n"/>
       <c r="K31" s="10" t="n"/>
       <c r="L31" s="11" t="n"/>
-      <c r="M31" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M31" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
         </is>
       </c>
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R31" s="10" t="n"/>
       <c r="S31" s="11" t="n"/>
-      <c r="T31" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
+      <c r="T31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U31" s="10" t="n"/>
       <c r="V31" s="10" t="n"/>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
+      <c r="Y31" s="17" t="inlineStr"/>
       <c r="Z31" s="10" t="n"/>
       <c r="AA31" s="10" t="n"/>
-      <c r="AB31" s="10" t="n"/>
-      <c r="AC31" s="10" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="17" t="inlineStr"/>
       <c r="AD31" s="10" t="n"/>
       <c r="AE31" s="11" t="n"/>
-      <c r="AF31" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF31" s="19" t="inlineStr">
+        <is>
+          <t>ソート方向（asc / desc。デフォルト: desc）</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -4423,196 +4658,27 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
-        </is>
-      </c>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="17" t="inlineStr"/>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
-      <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="11" t="n"/>
-      <c r="AF32" s="19" t="inlineStr">
-        <is>
-          <t>支店一覧</t>
-        </is>
-      </c>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="10" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" s="37" t="n"/>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>shiten_id</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="17" t="inlineStr"/>
-      <c r="U33" s="10" t="n"/>
-      <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
-      <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z33" s="10" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="10" t="n"/>
-      <c r="AC33" s="10" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="11" t="n"/>
-      <c r="AF33" s="19" t="inlineStr">
-        <is>
-          <t>支店ID</t>
-        </is>
-      </c>
-      <c r="AG33" s="10" t="n"/>
-      <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
-      <c r="AK33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z34" s="10" t="n"/>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
-      <c r="AC34" s="10" t="n"/>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="19" t="inlineStr">
-        <is>
-          <t>JA ID</t>
-        </is>
-      </c>
-      <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="10" t="n"/>
-      <c r="AI34" s="10" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" s="38" t="n"/>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>shiten_code</t>
-        </is>
-      </c>
+    <row r="32" ht="19.5" customHeight="1"/>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19.5" customHeight="1"/>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
@@ -4621,29 +4687,33 @@
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="11" t="n"/>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
       <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q35" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R35" s="10" t="n"/>
       <c r="S35" s="11" t="n"/>
-      <c r="T35" s="17" t="inlineStr"/>
+      <c r="T35" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U35" s="10" t="n"/>
       <c r="V35" s="10" t="n"/>
       <c r="W35" s="10" t="n"/>
       <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y35" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z35" s="10" t="n"/>
@@ -4652,9 +4722,9 @@
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="19" t="inlineStr">
-        <is>
-          <t>支店コード</t>
+      <c r="AF35" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -4665,14 +4735,14 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>shiten_name</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n"/>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
@@ -4683,7 +4753,7 @@
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
@@ -4691,7 +4761,7 @@
       <c r="P36" s="11" t="n"/>
       <c r="Q36" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R36" s="10" t="n"/>
@@ -4714,7 +4784,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>支店名称</t>
+          <t>支店一覧</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4725,12 +4795,12 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C37" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C37" s="37" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>shiten_name_kana</t>
+          <t>shiten_id</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -4743,7 +4813,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -4774,7 +4844,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>支店名称（カナ）</t>
+          <t>支店ID</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4785,12 +4855,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>kinyu_shiten_flg</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4803,7 +4873,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -4834,7 +4904,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>金融機関支店フラグ</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4845,12 +4915,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>shiten_code</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4863,7 +4933,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -4894,7 +4964,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>支店コード</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -4905,12 +4975,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>shiten_name</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -4954,7 +5024,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>管理支店名（m_kanri_shitenからJOIN）</t>
+          <t>支店名称</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -4965,12 +5035,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>jastem_toriatsukai_tenpo_code</t>
+          <t>shiten_name_kana</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -5014,7 +5084,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_データ送信取扱店舗コード ※空文字許容</t>
+          <t>支店名称（カナ）</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5025,12 +5095,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>jastem_tenpo_name</t>
+          <t>kinyu_shiten_flg</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -5043,7 +5113,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -5074,7 +5144,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_店舗名 ※空文字許容</t>
+          <t>金融機関支店フラグ</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5085,12 +5155,12 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>jastem_tyokin_shubetsu</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5103,7 +5173,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -5134,7 +5204,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_貯金種別 ※空文字許容</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5145,12 +5215,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>jastem_koza_no</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5194,7 +5264,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_口座番号 ※空文字許容</t>
+          <t>管理支店名（m_kanri_shitenからJOIN）</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5205,12 +5275,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>jastem_toriatsukai_tenpo_code</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5254,7 +5324,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>備考※空文字許容</t>
+          <t>JASTEM_データ送信取扱店舗コード ※空文字許容</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5265,12 +5335,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>jastem_tenpo_name</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5296,11 +5366,7 @@
       </c>
       <c r="R46" s="10" t="n"/>
       <c r="S46" s="11" t="n"/>
-      <c r="T46" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T46" s="17" t="inlineStr"/>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
       <c r="W46" s="10" t="n"/>
@@ -5318,7 +5384,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>JASTEM_店舗名 ※空文字許容</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -5329,12 +5395,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="C47" s="39" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>jastem_tyokin_shubetsu</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -5360,18 +5426,14 @@
       </c>
       <c r="R47" s="10" t="n"/>
       <c r="S47" s="11" t="n"/>
-      <c r="T47" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T47" s="17" t="inlineStr"/>
       <c r="U47" s="10" t="n"/>
       <c r="V47" s="10" t="n"/>
       <c r="W47" s="10" t="n"/>
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -5382,7 +5444,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>JASTEM_貯金種別 ※空文字許容</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -5393,14 +5455,14 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>jastem_koza_no</t>
+        </is>
+      </c>
       <c r="E48" s="10" t="n"/>
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="10" t="n"/>
@@ -5411,7 +5473,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -5442,7 +5504,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>JASTEM_口座番号 ※空文字許容</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -5453,12 +5515,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C49" s="37" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -5471,7 +5533,7 @@
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N49" s="10" t="n"/>
@@ -5502,7 +5564,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>備考※空文字許容</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -5513,12 +5575,12 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E50" s="10" t="n"/>
@@ -5531,7 +5593,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -5544,7 +5606,11 @@
       </c>
       <c r="R50" s="10" t="n"/>
       <c r="S50" s="11" t="n"/>
-      <c r="T50" s="17" t="inlineStr"/>
+      <c r="T50" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
       <c r="W50" s="10" t="n"/>
@@ -5562,7 +5628,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>現在のページ番号</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -5573,12 +5639,12 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C51" s="38" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="C51" s="39" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -5591,7 +5657,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -5604,14 +5670,18 @@
       </c>
       <c r="R51" s="10" t="n"/>
       <c r="S51" s="11" t="n"/>
-      <c r="T51" s="17" t="inlineStr"/>
+      <c r="T51" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U51" s="10" t="n"/>
       <c r="V51" s="10" t="n"/>
       <c r="W51" s="10" t="n"/>
       <c r="X51" s="11" t="n"/>
       <c r="Y51" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z51" s="10" t="n"/>
@@ -5622,7 +5692,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -5633,14 +5703,14 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C52" s="39" t="n"/>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>total_pages</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n"/>
       <c r="E52" s="10" t="n"/>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
@@ -5651,7 +5721,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -5682,7 +5752,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -5691,21 +5761,136 @@
       <c r="AJ52" s="10" t="n"/>
       <c r="AK52" s="11" t="n"/>
     </row>
-    <row r="53" ht="19.5" customHeight="1"/>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="B54" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C53" s="37" t="n"/>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="11" t="n"/>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="17" t="inlineStr"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="11" t="n"/>
+      <c r="Y53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="11" t="n"/>
+      <c r="AF53" s="19" t="inlineStr">
+        <is>
+          <t>総件数</t>
+        </is>
+      </c>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="11" t="n"/>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="11" t="n"/>
+      <c r="T54" s="17" t="inlineStr"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="11" t="n"/>
+      <c r="Y54" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="11" t="n"/>
+      <c r="AF54" s="19" t="inlineStr">
+        <is>
+          <t>現在のページ番号</t>
+        </is>
+      </c>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/shiten?shiten_name=本店&amp;page=1&amp;per_page=20&amp;sort_by=shiten_code&amp;sort_order=asc</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="n"/>
+      <c r="B55" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C55" s="38" t="n"/>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
       <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
@@ -5713,42 +5898,167 @@
       <c r="I55" s="10" t="n"/>
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
-      <c r="L55" s="10" t="n"/>
-      <c r="M55" s="10" t="n"/>
+      <c r="L55" s="11" t="n"/>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
-      <c r="P55" s="10" t="n"/>
-      <c r="Q55" s="10" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R55" s="10" t="n"/>
-      <c r="S55" s="10" t="n"/>
-      <c r="T55" s="10" t="n"/>
+      <c r="S55" s="11" t="n"/>
+      <c r="T55" s="17" t="inlineStr"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
-      <c r="X55" s="10" t="n"/>
-      <c r="Y55" s="10" t="n"/>
+      <c r="X55" s="11" t="n"/>
+      <c r="Y55" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z55" s="10" t="n"/>
       <c r="AA55" s="10" t="n"/>
       <c r="AB55" s="10" t="n"/>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="10" t="n"/>
-      <c r="AF55" s="10" t="n"/>
+      <c r="AE55" s="11" t="n"/>
+      <c r="AF55" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数</t>
+        </is>
+      </c>
       <c r="AG55" s="10" t="n"/>
       <c r="AH55" s="10" t="n"/>
       <c r="AI55" s="10" t="n"/>
       <c r="AJ55" s="10" t="n"/>
       <c r="AK55" s="11" t="n"/>
     </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="B57" s="40" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="C56" s="39" t="n"/>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="10" t="n"/>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="11" t="n"/>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="11" t="n"/>
+      <c r="Q56" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="11" t="n"/>
+      <c r="T56" s="17" t="inlineStr"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="11" t="n"/>
+      <c r="Y56" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="10" t="n"/>
+      <c r="AD56" s="10" t="n"/>
+      <c r="AE56" s="11" t="n"/>
+      <c r="AF56" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
+      <c r="AG56" s="10" t="n"/>
+      <c r="AH56" s="10" t="n"/>
+      <c r="AI56" s="10" t="n"/>
+      <c r="AJ56" s="10" t="n"/>
+      <c r="AK56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1"/>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="B58" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/shiten?shiten_code=S0&amp;shiten_name=本店&amp;kanri_shiten_id=1&amp;jastem_toriatsukai_tenpo_code=001&amp;kinyu_shiten_flg=true&amp;page=1&amp;per_page=20&amp;sort_by=updated_at&amp;sort_order=desc</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="10" t="n"/>
+      <c r="X59" s="10" t="n"/>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="10" t="n"/>
+      <c r="AE59" s="10" t="n"/>
+      <c r="AF59" s="10" t="n"/>
+      <c r="AG59" s="10" t="n"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="10" t="n"/>
+      <c r="AJ59" s="10" t="n"/>
+      <c r="AK59" s="11" t="n"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="B61" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="409" customHeight="1">
-      <c r="C58" s="19" t="inlineStr">
+    <row r="62" ht="409" customHeight="1">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -5796,50 +6106,50 @@
 }</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
-      <c r="Q58" s="10" t="n"/>
-      <c r="R58" s="10" t="n"/>
-      <c r="S58" s="10" t="n"/>
-      <c r="T58" s="10" t="n"/>
-      <c r="U58" s="10" t="n"/>
-      <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
-      <c r="X58" s="10" t="n"/>
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AA58" s="10" t="n"/>
-      <c r="AB58" s="10" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="10" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="10" t="n"/>
-      <c r="AK58" s="11" t="n"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="B60" s="40" t="inlineStr">
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="10" t="n"/>
+      <c r="X62" s="10" t="n"/>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="10" t="n"/>
+      <c r="AE62" s="10" t="n"/>
+      <c r="AF62" s="10" t="n"/>
+      <c r="AG62" s="10" t="n"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="10" t="n"/>
+      <c r="AJ62" s="10" t="n"/>
+      <c r="AK62" s="11" t="n"/>
+    </row>
+    <row r="64" ht="19.5" customHeight="1">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="72" customHeight="1">
-      <c r="C61" s="19" t="inlineStr">
+    <row r="65" ht="72" customHeight="1">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "BAD_REQUEST",
@@ -5847,50 +6157,50 @@
 }</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
-      <c r="U61" s="10" t="n"/>
-      <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-      <c r="AA61" s="10" t="n"/>
-      <c r="AB61" s="10" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="10" t="n"/>
-      <c r="AK61" s="11" t="n"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="10" t="n"/>
+      <c r="X65" s="10" t="n"/>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="10" t="n"/>
+      <c r="AE65" s="10" t="n"/>
+      <c r="AF65" s="10" t="n"/>
+      <c r="AG65" s="10" t="n"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="10" t="n"/>
+      <c r="AJ65" s="10" t="n"/>
+      <c r="AK65" s="11" t="n"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="B67" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="72" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
+    <row r="68" ht="72" customHeight="1">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -5898,50 +6208,50 @@
 }</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-      <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
-      <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
-      <c r="U64" s="10" t="n"/>
-      <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-      <c r="AA64" s="10" t="n"/>
-      <c r="AB64" s="10" t="n"/>
-      <c r="AC64" s="10" t="n"/>
-      <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
-      <c r="AG64" s="10" t="n"/>
-      <c r="AH64" s="10" t="n"/>
-      <c r="AI64" s="10" t="n"/>
-      <c r="AJ64" s="10" t="n"/>
-      <c r="AK64" s="11" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="B66" s="40" t="inlineStr">
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="10" t="n"/>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="10" t="n"/>
+      <c r="X68" s="10" t="n"/>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="10" t="n"/>
+      <c r="AE68" s="10" t="n"/>
+      <c r="AF68" s="10" t="n"/>
+      <c r="AG68" s="10" t="n"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="10" t="n"/>
+      <c r="AJ68" s="10" t="n"/>
+      <c r="AK68" s="11" t="n"/>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="B70" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="72" customHeight="1">
-      <c r="C67" s="19" t="inlineStr">
+    <row r="71" ht="72" customHeight="1">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -5949,50 +6259,50 @@
 }</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="10" t="n"/>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="10" t="n"/>
-      <c r="U67" s="10" t="n"/>
-      <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
-      <c r="X67" s="10" t="n"/>
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-      <c r="AA67" s="10" t="n"/>
-      <c r="AB67" s="10" t="n"/>
-      <c r="AC67" s="10" t="n"/>
-      <c r="AD67" s="10" t="n"/>
-      <c r="AE67" s="10" t="n"/>
-      <c r="AF67" s="10" t="n"/>
-      <c r="AG67" s="10" t="n"/>
-      <c r="AH67" s="10" t="n"/>
-      <c r="AI67" s="10" t="n"/>
-      <c r="AJ67" s="10" t="n"/>
-      <c r="AK67" s="11" t="n"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="B69" s="40" t="inlineStr">
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="10" t="n"/>
+      <c r="X71" s="10" t="n"/>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="10" t="n"/>
+      <c r="AE71" s="10" t="n"/>
+      <c r="AF71" s="10" t="n"/>
+      <c r="AG71" s="10" t="n"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="10" t="n"/>
+      <c r="AJ71" s="10" t="n"/>
+      <c r="AK71" s="11" t="n"/>
+    </row>
+    <row r="73" ht="19.5" customHeight="1">
+      <c r="B73" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="19" t="inlineStr">
+    <row r="74" ht="72" customHeight="1">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -6000,327 +6310,388 @@
 }</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="72" ht="19.5" customHeight="1"/>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="10" t="n"/>
+      <c r="J74" s="10" t="n"/>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="10" t="n"/>
+      <c r="Q74" s="10" t="n"/>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
+      <c r="W74" s="10" t="n"/>
+      <c r="X74" s="10" t="n"/>
+      <c r="Y74" s="10" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="10" t="n"/>
+      <c r="AD74" s="10" t="n"/>
+      <c r="AE74" s="10" t="n"/>
+      <c r="AF74" s="10" t="n"/>
+      <c r="AG74" s="10" t="n"/>
+      <c r="AH74" s="10" t="n"/>
+      <c r="AI74" s="10" t="n"/>
+      <c r="AJ74" s="10" t="n"/>
+      <c r="AK74" s="11" t="n"/>
+    </row>
+    <row r="76" ht="19.5" customHeight="1"/>
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="B74" s="27" t="inlineStr">
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>shiten_name：文字列型チェック、最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="D77" s="41" t="inlineStr">
-        <is>
-          <t>page：数値型チェック、≧ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="D78" s="41" t="inlineStr">
-        <is>
-          <t>per_page：数値型チェック、1〜100</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>sort_by：許可値チェック（shiten_code, shiten_name, kanri_shiten_name）</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="D80" s="41" t="inlineStr">
         <is>
-          <t>sort_order：許可値チェック（asc, desc）</t>
+          <t>shiten_code：文字列型チェック、最大3桁</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>デフォルト値の適用：</t>
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>shiten_name：文字列型チェック、最大100桁</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>page：未指定の場合、1</t>
+          <t>kanri_shiten_id：整数型チェック</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="D83" s="41" t="inlineStr">
         <is>
-          <t>per_page：未指定の場合、20</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
+          <t>jastem_toriatsukai_tenpo_code：文字列型チェック、最大3桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
-          <t>sort_by：未指定の場合、shiten_code</t>
+          <t>kinyu_shiten_flg：Boolean型チェック（クエリ文字列 'true' / 'false' をBooleanに変換、空文字は未指定として扱う）</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>sort_order：未指定の場合、asc</t>
+          <t>page：数値型チェック、≧ 1</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
+      <c r="D86" s="41" t="inlineStr">
+        <is>
+          <t>per_page：数値型チェック、1〜100</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request (`BAD_REQUEST`) を返却する。</t>
+          <t>sort_by：許可値チェック（shiten_code, shiten_name, kanri_shiten_name, updated_at）</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="B88" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="D88" s="41" t="inlineStr">
+        <is>
+          <t>sort_order：許可値チェック（asc, desc）</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
+          <t>デフォルト値の適用：</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="D90" s="41" t="inlineStr">
+        <is>
+          <t>page：未指定の場合、1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>per_page：未指定の場合、20</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>sort_by：未指定の場合、updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>sort_order：未指定の場合、desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="D95" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request (`BAD_REQUEST`) を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
+        <is>
           <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`shiten.view` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="36" customHeight="1">
-      <c r="D92" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="B94" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="C96" s="41" t="inlineStr">
-        <is>
-          <t>基本条件：</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="D97" s="41" t="inlineStr">
-        <is>
-          <t>スコープ制御（ja_id = user.ja_id）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="D98" s="41" t="inlineStr">
-        <is>
-          <t>論理削除除外（deleted_at IS NULL）</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>検索条件：</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
+          <t>権限チェック：`shiten.view` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
       <c r="D100" s="41" t="inlineStr">
         <is>
-          <t>shiten_name：部分一致（ILIKE '%value%'）</t>
+          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="D101" s="41" t="inlineStr">
-        <is>
-          <t>sort_by / sort_order：ソート適用</t>
+      <c r="C101" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="B102" s="27" t="inlineStr">
         <is>
-          <t>4.4 データ件数の取得</t>
+          <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="C103" s="41" t="inlineStr">
         <is>
-          <t>条件に一致する総件数を取得する。</t>
+          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="C104" s="41" t="inlineStr">
         <is>
+          <t>基本条件：</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="D105" s="41" t="inlineStr">
+        <is>
+          <t>スコープ制御（ja_id = user.ja_id）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="D106" s="41" t="inlineStr">
+        <is>
+          <t>論理削除除外（deleted_at IS NULL）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="C107" s="41" t="inlineStr">
+        <is>
+          <t>検索条件：</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="D108" s="41" t="inlineStr">
+        <is>
+          <t>shiten_code：部分一致（ILIKE '%value%'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="D109" s="41" t="inlineStr">
+        <is>
+          <t>shiten_name：部分一致（ILIKE '%value%'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="D110" s="41" t="inlineStr">
+        <is>
+          <t>kanri_shiten_id：完全一致（= :value）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="D111" s="41" t="inlineStr">
+        <is>
+          <t>jastem_toriatsukai_tenpo_code：部分一致（ILIKE '%value%'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>kinyu_shiten_flg：完全一致（= :value）。**未指定（全選択）の場合は絞り込みを適用しない**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="D113" s="41" t="inlineStr">
+        <is>
+          <t>sort_by / sort_order：ソート適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>4.4 データ件数の取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="C115" s="41" t="inlineStr">
+        <is>
+          <t>条件に一致する総件数を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="C116" s="41" t="inlineStr">
+        <is>
           <t>meta.total に使用する。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="90" customHeight="1">
-      <c r="C105" s="42" t="inlineStr">
+    <row r="117" ht="180" customHeight="1">
+      <c r="C117" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
 FROM m_shiten
 WHERE ja_id = :ja_id
   AND deleted_at IS NULL
-  AND (:shiten_name IS NULL OR shiten_name ILIKE '%' || :shiten_name || '%')</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="n"/>
-      <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
-      <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
-      <c r="L105" s="10" t="n"/>
-      <c r="M105" s="10" t="n"/>
-      <c r="N105" s="10" t="n"/>
-      <c r="O105" s="10" t="n"/>
-      <c r="P105" s="10" t="n"/>
-      <c r="Q105" s="10" t="n"/>
-      <c r="R105" s="10" t="n"/>
-      <c r="S105" s="10" t="n"/>
-      <c r="T105" s="10" t="n"/>
-      <c r="U105" s="10" t="n"/>
-      <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n"/>
-      <c r="X105" s="10" t="n"/>
-      <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="10" t="n"/>
-      <c r="AA105" s="10" t="n"/>
-      <c r="AB105" s="10" t="n"/>
-      <c r="AC105" s="10" t="n"/>
-      <c r="AD105" s="10" t="n"/>
-      <c r="AE105" s="10" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
-      <c r="AI105" s="10" t="n"/>
-      <c r="AJ105" s="10" t="n"/>
-      <c r="AK105" s="11" t="n"/>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="B106" s="27" t="inlineStr">
+  AND (:shiten_code IS NULL OR shiten_code ILIKE '%' || :shiten_code || '%')
+  AND (:shiten_name IS NULL OR shiten_name ILIKE '%' || :shiten_name || '%')
+  AND (:kanri_shiten_id IS NULL OR kanri_shiten_id = :kanri_shiten_id)
+  AND (:jastem_toriatsukai_tenpo_code IS NULL
+       OR jastem_toriatsukai_tenpo_code ILIKE '%' || :jastem_toriatsukai_tenpo_code || '%')
+  AND (:kinyu_shiten_flg IS NULL OR kinyu_shiten_flg = :kinyu_shiten_flg)</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="n"/>
+      <c r="J117" s="10" t="n"/>
+      <c r="K117" s="10" t="n"/>
+      <c r="L117" s="10" t="n"/>
+      <c r="M117" s="10" t="n"/>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
+      <c r="P117" s="10" t="n"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
+      <c r="U117" s="10" t="n"/>
+      <c r="V117" s="10" t="n"/>
+      <c r="W117" s="10" t="n"/>
+      <c r="X117" s="10" t="n"/>
+      <c r="Y117" s="10" t="n"/>
+      <c r="Z117" s="10" t="n"/>
+      <c r="AA117" s="10" t="n"/>
+      <c r="AB117" s="10" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="10" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="10" t="n"/>
+      <c r="AK117" s="11" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="B118" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="C107" s="41" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="C119" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行してデータを取得する。</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="270" customHeight="1">
-      <c r="C108" s="42" t="inlineStr">
+    <row r="120" ht="360" customHeight="1">
+      <c r="C120" s="42" t="inlineStr">
         <is>
           <t>SELECT s.shiten_id, s.ja_id, s.shiten_code, s.shiten_name, s.shiten_name_kana,
        s.kinyu_shiten_flg, s.kanri_shiten_id, ks.kanri_shiten_name,
@@ -6333,387 +6704,428 @@
   AND ks.deleted_at IS NULL
 WHERE s.ja_id = :ja_id
   AND s.deleted_at IS NULL
+  AND (:shiten_code IS NULL OR s.shiten_code ILIKE '%' || :shiten_code || '%')
   AND (:shiten_name IS NULL OR s.shiten_name ILIKE '%' || :shiten_name || '%')
+  AND (:kanri_shiten_id IS NULL OR s.kanri_shiten_id = :kanri_shiten_id)
+  AND (:jastem_toriatsukai_tenpo_code IS NULL
+       OR s.jastem_toriatsukai_tenpo_code ILIKE '%' || :jastem_toriatsukai_tenpo_code || '%')
+  AND (:kinyu_shiten_flg IS NULL OR s.kinyu_shiten_flg = :kinyu_shiten_flg)
 ORDER BY {sort_target} {sort_order}
 LIMIT :per_page
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n"/>
-      <c r="E108" s="10" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="10" t="n"/>
-      <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
-      <c r="J108" s="10" t="n"/>
-      <c r="K108" s="10" t="n"/>
-      <c r="L108" s="10" t="n"/>
-      <c r="M108" s="10" t="n"/>
-      <c r="N108" s="10" t="n"/>
-      <c r="O108" s="10" t="n"/>
-      <c r="P108" s="10" t="n"/>
-      <c r="Q108" s="10" t="n"/>
-      <c r="R108" s="10" t="n"/>
-      <c r="S108" s="10" t="n"/>
-      <c r="T108" s="10" t="n"/>
-      <c r="U108" s="10" t="n"/>
-      <c r="V108" s="10" t="n"/>
-      <c r="W108" s="10" t="n"/>
-      <c r="X108" s="10" t="n"/>
-      <c r="Y108" s="10" t="n"/>
-      <c r="Z108" s="10" t="n"/>
-      <c r="AA108" s="10" t="n"/>
-      <c r="AB108" s="10" t="n"/>
-      <c r="AC108" s="10" t="n"/>
-      <c r="AD108" s="10" t="n"/>
-      <c r="AE108" s="10" t="n"/>
-      <c r="AF108" s="10" t="n"/>
-      <c r="AG108" s="10" t="n"/>
-      <c r="AH108" s="10" t="n"/>
-      <c r="AI108" s="10" t="n"/>
-      <c r="AJ108" s="10" t="n"/>
-      <c r="AK108" s="11" t="n"/>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="B109" s="27" t="inlineStr">
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="10" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="10" t="n"/>
+      <c r="J120" s="10" t="n"/>
+      <c r="K120" s="10" t="n"/>
+      <c r="L120" s="10" t="n"/>
+      <c r="M120" s="10" t="n"/>
+      <c r="N120" s="10" t="n"/>
+      <c r="O120" s="10" t="n"/>
+      <c r="P120" s="10" t="n"/>
+      <c r="Q120" s="10" t="n"/>
+      <c r="R120" s="10" t="n"/>
+      <c r="S120" s="10" t="n"/>
+      <c r="T120" s="10" t="n"/>
+      <c r="U120" s="10" t="n"/>
+      <c r="V120" s="10" t="n"/>
+      <c r="W120" s="10" t="n"/>
+      <c r="X120" s="10" t="n"/>
+      <c r="Y120" s="10" t="n"/>
+      <c r="Z120" s="10" t="n"/>
+      <c r="AA120" s="10" t="n"/>
+      <c r="AB120" s="10" t="n"/>
+      <c r="AC120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="10" t="n"/>
+      <c r="AF120" s="10" t="n"/>
+      <c r="AG120" s="10" t="n"/>
+      <c r="AH120" s="10" t="n"/>
+      <c r="AI120" s="10" t="n"/>
+      <c r="AJ120" s="10" t="n"/>
+      <c r="AK120" s="11" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="B121" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="C110" s="41" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="C122" s="41" t="inlineStr">
         <is>
           <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="C111" s="41" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="C123" s="41" t="inlineStr">
         <is>
           <t>meta の計算：</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="D112" s="41" t="inlineStr">
+    <row r="124" ht="18" customHeight="1">
+      <c r="D124" s="41" t="inlineStr">
         <is>
           <t>total：4.4 で取得した総件数</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="D113" s="41" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="D125" s="41" t="inlineStr">
         <is>
           <t>page：リクエストの page 値</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="D114" s="41" t="inlineStr">
+    <row r="126" ht="18" customHeight="1">
+      <c r="D126" s="41" t="inlineStr">
         <is>
           <t>per_page：リクエストの per_page 値</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="D115" s="41" t="inlineStr">
+    <row r="127" ht="18" customHeight="1">
+      <c r="D127" s="41" t="inlineStr">
         <is>
           <t>total_pages：CEIL(total / per_page)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="B116" s="27" t="inlineStr">
+    <row r="128" ht="18" customHeight="1">
+      <c r="B128" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="C117" s="41" t="inlineStr">
+    <row r="129" ht="18" customHeight="1">
+      <c r="C129" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="275">
-    <mergeCell ref="B102:AK102"/>
+  <mergeCells count="311">
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="T53:X53"/>
+    <mergeCell ref="D56:L56"/>
+    <mergeCell ref="T55:X55"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C129:AK129"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="D124:AK124"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="T37:X37"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="D126:AK126"/>
+    <mergeCell ref="T38:X38"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="Y53:AE53"/>
+    <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="Q48:S48"/>
+    <mergeCell ref="B14:I18"/>
+    <mergeCell ref="Y55:AE55"/>
+    <mergeCell ref="C117:AK117"/>
+    <mergeCell ref="A77:AK77"/>
+    <mergeCell ref="T40:X40"/>
+    <mergeCell ref="D81:AK81"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="C115:AK115"/>
+    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="T45:X45"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="Y56:AE56"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="T51:X51"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="AF56:AK56"/>
+    <mergeCell ref="AF43:AK43"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D105:AK105"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="C119:AK119"/>
+    <mergeCell ref="Q54:S54"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="B121:AK121"/>
+    <mergeCell ref="B96:AK96"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="Y38:AE38"/>
+    <mergeCell ref="D100:AK100"/>
+    <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="Y51:AE51"/>
+    <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="D108:AK108"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C71:AK71"/>
+    <mergeCell ref="D95:AK95"/>
+    <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Y22:AB22"/>
+    <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="M46:P46"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="M56:P56"/>
+    <mergeCell ref="D113:AK113"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="T22:X22"/>
+    <mergeCell ref="B114:AK114"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="T46:X46"/>
+    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="D49:L49"/>
+    <mergeCell ref="T48:X48"/>
+    <mergeCell ref="C62:AK62"/>
+    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="A20:AK20"/>
+    <mergeCell ref="C89:AK89"/>
+    <mergeCell ref="AF42:AK42"/>
+    <mergeCell ref="C116:AK116"/>
+    <mergeCell ref="B67:I67"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="D54:L54"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="Y35:AE35"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="T56:X56"/>
+    <mergeCell ref="T43:X43"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="T36:X36"/>
+    <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="A33:AK33"/>
+    <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D44:L44"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="C53:C56"/>
+    <mergeCell ref="M42:P42"/>
     <mergeCell ref="J11:AK11"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="D78:AK78"/>
     <mergeCell ref="Y36:AE36"/>
-    <mergeCell ref="T24:X24"/>
     <mergeCell ref="D87:AK87"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="Y45:AE45"/>
-    <mergeCell ref="T33:X33"/>
-    <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M32:P32"/>
-    <mergeCell ref="N18:AK18"/>
-    <mergeCell ref="C86:AK86"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="M46:P46"/>
-    <mergeCell ref="C58:AK58"/>
-    <mergeCell ref="N17:AK17"/>
-    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="B70:I70"/>
     <mergeCell ref="D82:AK82"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="D113:AK113"/>
-    <mergeCell ref="Y52:AE52"/>
-    <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="AF50:AK50"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C91:AK91"/>
-    <mergeCell ref="D33:L33"/>
-    <mergeCell ref="D115:AK115"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D51:L51"/>
-    <mergeCell ref="AF52:AK52"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C75:AK75"/>
-    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
-    <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="AF36:AK36"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
-    <mergeCell ref="T22:X22"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="T31:X31"/>
-    <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="C95:AK95"/>
-    <mergeCell ref="D101:AK101"/>
-    <mergeCell ref="D34:L34"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="D77:AK77"/>
-    <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="C70:AK70"/>
-    <mergeCell ref="T37:X37"/>
-    <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="C49:C52"/>
-    <mergeCell ref="M33:P33"/>
-    <mergeCell ref="M45:P45"/>
-    <mergeCell ref="C48:L48"/>
-    <mergeCell ref="D112:AK112"/>
-    <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="T38:X38"/>
-    <mergeCell ref="M47:P47"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="T28:X28"/>
+    <mergeCell ref="T30:X30"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="D53:L53"/>
     <mergeCell ref="D47:L47"/>
-    <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="C104:AK104"/>
-    <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="D114:AK114"/>
-    <mergeCell ref="D37:L37"/>
-    <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="AF51:AK51"/>
-    <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="B116:AK116"/>
-    <mergeCell ref="D98:AK98"/>
-    <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="T54:X54"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="C24:L24"/>
-    <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="D39:L39"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="M44:P44"/>
-    <mergeCell ref="Q48:S48"/>
-    <mergeCell ref="B14:I18"/>
-    <mergeCell ref="D79:AK79"/>
+    <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="C117:AK117"/>
-    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="C99:AK99"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D38:L38"/>
-    <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="Y39:AE39"/>
-    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="D90:AK90"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="AF37:AK37"/>
-    <mergeCell ref="A2:I3"/>
-    <mergeCell ref="AF24:AK24"/>
-    <mergeCell ref="Y26:AB26"/>
-    <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B106:AK106"/>
+    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="D76:AK76"/>
-    <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="Q51:S51"/>
-    <mergeCell ref="M27:P27"/>
-    <mergeCell ref="D52:L52"/>
+    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="M36:P36"/>
-    <mergeCell ref="Y37:AE37"/>
-    <mergeCell ref="T39:X39"/>
-    <mergeCell ref="D49:L49"/>
-    <mergeCell ref="C81:AK81"/>
-    <mergeCell ref="Y27:AB27"/>
-    <mergeCell ref="T48:X48"/>
-    <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="C96:AK96"/>
-    <mergeCell ref="T32:X32"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="T45:X45"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="T50:X50"/>
+    <mergeCell ref="T44:X44"/>
+    <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="D55:L55"/>
+    <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="D80:AK80"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="C120:AK120"/>
+    <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="Q55:S55"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="D91:AK91"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="D106:AK106"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="D93:AK93"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="M52:P52"/>
+    <mergeCell ref="D109:AK109"/>
+    <mergeCell ref="AF46:AK46"/>
+    <mergeCell ref="D84:AK84"/>
+    <mergeCell ref="Q53:S53"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="D111:AK111"/>
+    <mergeCell ref="AF48:AK48"/>
+    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="B102:AK102"/>
+    <mergeCell ref="N18:AK18"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="B128:AK128"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="C37:C51"/>
+    <mergeCell ref="M45:P45"/>
+    <mergeCell ref="D125:AK125"/>
+    <mergeCell ref="D112:AK112"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="C101:AK101"/>
+    <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="D127:AK127"/>
+    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="B78:AK78"/>
+    <mergeCell ref="M44:P44"/>
+    <mergeCell ref="B118:AK118"/>
+    <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="C36:L36"/>
+    <mergeCell ref="Q51:S51"/>
+    <mergeCell ref="T39:X39"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="J7:AK7"/>
     <mergeCell ref="T47:X47"/>
-    <mergeCell ref="D92:AK92"/>
-    <mergeCell ref="A20:AK20"/>
-    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="M53:P53"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="C107:AK107"/>
-    <mergeCell ref="A29:AK29"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="Q49:S49"/>
-    <mergeCell ref="T50:X50"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C64:AK64"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="AF40:AK40"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="M55:P55"/>
     <mergeCell ref="M48:P48"/>
-    <mergeCell ref="T51:X51"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="A73:AK73"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="T41:X41"/>
-    <mergeCell ref="Y35:AE35"/>
-    <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="C105:AK105"/>
-    <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="B94:AK94"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="C89:AK89"/>
-    <mergeCell ref="M40:P40"/>
-    <mergeCell ref="T43:X43"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
-    <mergeCell ref="N16:AK16"/>
-    <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="T36:X36"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="C67:AK67"/>
-    <mergeCell ref="D97:AK97"/>
-    <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="M41:P41"/>
-    <mergeCell ref="C33:C47"/>
-    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q40:S40"/>
     <mergeCell ref="M38:P38"/>
-    <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="T35:X35"/>
-    <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="Y32:AE32"/>
+    <mergeCell ref="B58:I58"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D83:AK83"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="B88:AK88"/>
-    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="Y38:AE38"/>
-    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D85:AK85"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="M52:P52"/>
-    <mergeCell ref="D100:AK100"/>
-    <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="B74:AK74"/>
-    <mergeCell ref="AF46:AK46"/>
-    <mergeCell ref="D84:AK84"/>
-    <mergeCell ref="D50:L50"/>
-    <mergeCell ref="D44:L44"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="Y51:AE51"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C90:AK90"/>
-    <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="AF48:AK48"/>
-    <mergeCell ref="C31:L31"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
-    <mergeCell ref="C110:AK110"/>
-    <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="Q52:S52"/>
-    <mergeCell ref="B109:AK109"/>
-    <mergeCell ref="Y34:AE34"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Y52:AE52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6725,7 +7137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK96"/>
+  <dimension ref="A1:AK97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6886,7 +7298,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7406,7 +7818,7 @@
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>この画面へのアクセス権限がありません</t>
+          <t>この画面へのアクセス権限がありません／このデータへのアクセス権限がありません</t>
         </is>
       </c>
       <c r="O17" s="10" t="n"/>
@@ -8448,21 +8860,28 @@
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>DataScope チェック（2段階）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>4.4 関連データの存在チェック</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>以下のテーブルに関連レコードが存在するか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="72" customHeight="1">
-      <c r="C80" s="42" t="inlineStr">
+    <row r="81" ht="72" customHeight="1">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">-- 購読者の支店参照チェック
 SELECT COUNT(*) FROM t_dokusya
@@ -8470,78 +8889,78 @@
 </t>
         </is>
       </c>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="10" t="n"/>
-      <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="10" t="n"/>
-      <c r="M80" s="10" t="n"/>
-      <c r="N80" s="10" t="n"/>
-      <c r="O80" s="10" t="n"/>
-      <c r="P80" s="10" t="n"/>
-      <c r="Q80" s="10" t="n"/>
-      <c r="R80" s="10" t="n"/>
-      <c r="S80" s="10" t="n"/>
-      <c r="T80" s="10" t="n"/>
-      <c r="U80" s="10" t="n"/>
-      <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n"/>
-      <c r="X80" s="10" t="n"/>
-      <c r="Y80" s="10" t="n"/>
-      <c r="Z80" s="10" t="n"/>
-      <c r="AA80" s="10" t="n"/>
-      <c r="AB80" s="10" t="n"/>
-      <c r="AC80" s="10" t="n"/>
-      <c r="AD80" s="10" t="n"/>
-      <c r="AE80" s="10" t="n"/>
-      <c r="AF80" s="10" t="n"/>
-      <c r="AG80" s="10" t="n"/>
-      <c r="AH80" s="10" t="n"/>
-      <c r="AI80" s="10" t="n"/>
-      <c r="AJ80" s="10" t="n"/>
-      <c r="AK80" s="11" t="n"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>いずれかに関連レコードが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="D83" s="41" t="inlineStr">
         <is>
           <t>HTTP 409 Conflict (`CONFLICT`) を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="B83" s="27" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>4.5 論理削除の実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>削除前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="C85" s="41" t="inlineStr">
         <is>
+          <t>削除前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
           <t>以下のSQLを実行して論理削除を行う。</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="108" customHeight="1">
-      <c r="C86" s="42" t="inlineStr">
+    <row r="87" ht="108" customHeight="1">
+      <c r="C87" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_shiten
 SET deleted_at = NOW(),
@@ -8551,57 +8970,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n"/>
-      <c r="E86" s="10" t="n"/>
-      <c r="F86" s="10" t="n"/>
-      <c r="G86" s="10" t="n"/>
-      <c r="H86" s="10" t="n"/>
-      <c r="I86" s="10" t="n"/>
-      <c r="J86" s="10" t="n"/>
-      <c r="K86" s="10" t="n"/>
-      <c r="L86" s="10" t="n"/>
-      <c r="M86" s="10" t="n"/>
-      <c r="N86" s="10" t="n"/>
-      <c r="O86" s="10" t="n"/>
-      <c r="P86" s="10" t="n"/>
-      <c r="Q86" s="10" t="n"/>
-      <c r="R86" s="10" t="n"/>
-      <c r="S86" s="10" t="n"/>
-      <c r="T86" s="10" t="n"/>
-      <c r="U86" s="10" t="n"/>
-      <c r="V86" s="10" t="n"/>
-      <c r="W86" s="10" t="n"/>
-      <c r="X86" s="10" t="n"/>
-      <c r="Y86" s="10" t="n"/>
-      <c r="Z86" s="10" t="n"/>
-      <c r="AA86" s="10" t="n"/>
-      <c r="AB86" s="10" t="n"/>
-      <c r="AC86" s="10" t="n"/>
-      <c r="AD86" s="10" t="n"/>
-      <c r="AE86" s="10" t="n"/>
-      <c r="AF86" s="10" t="n"/>
-      <c r="AG86" s="10" t="n"/>
-      <c r="AH86" s="10" t="n"/>
-      <c r="AI86" s="10" t="n"/>
-      <c r="AJ86" s="10" t="n"/>
-      <c r="AK86" s="11" t="n"/>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="B87" s="27" t="inlineStr">
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>4.6 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
+    <row r="89" ht="18" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="216" customHeight="1">
-      <c r="C89" s="42" t="inlineStr">
+    <row r="90" ht="216" customHeight="1">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -8615,58 +9034,6 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="n"/>
-      <c r="E89" s="10" t="n"/>
-      <c r="F89" s="10" t="n"/>
-      <c r="G89" s="10" t="n"/>
-      <c r="H89" s="10" t="n"/>
-      <c r="I89" s="10" t="n"/>
-      <c r="J89" s="10" t="n"/>
-      <c r="K89" s="10" t="n"/>
-      <c r="L89" s="10" t="n"/>
-      <c r="M89" s="10" t="n"/>
-      <c r="N89" s="10" t="n"/>
-      <c r="O89" s="10" t="n"/>
-      <c r="P89" s="10" t="n"/>
-      <c r="Q89" s="10" t="n"/>
-      <c r="R89" s="10" t="n"/>
-      <c r="S89" s="10" t="n"/>
-      <c r="T89" s="10" t="n"/>
-      <c r="U89" s="10" t="n"/>
-      <c r="V89" s="10" t="n"/>
-      <c r="W89" s="10" t="n"/>
-      <c r="X89" s="10" t="n"/>
-      <c r="Y89" s="10" t="n"/>
-      <c r="Z89" s="10" t="n"/>
-      <c r="AA89" s="10" t="n"/>
-      <c r="AB89" s="10" t="n"/>
-      <c r="AC89" s="10" t="n"/>
-      <c r="AD89" s="10" t="n"/>
-      <c r="AE89" s="10" t="n"/>
-      <c r="AF89" s="10" t="n"/>
-      <c r="AG89" s="10" t="n"/>
-      <c r="AH89" s="10" t="n"/>
-      <c r="AI89" s="10" t="n"/>
-      <c r="AJ89" s="10" t="n"/>
-      <c r="AK89" s="11" t="n"/>
-    </row>
-    <row r="90" ht="234" customHeight="1">
-      <c r="C90" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "shiten_id": 5,
-  "ja_id": 1,
-  "shiten_code": "S05",
-  "shiten_name": "削除対象支店",
-  "shiten_name_kana": "サクジョタイショウシテン",
-  "kinyu_shiten_flg": false,
-  "kanri_shiten_id": 1,
-  "biko": "テスト用支店"
-}</t>
         </is>
       </c>
       <c r="D90" s="10" t="n"/>
@@ -8704,43 +9071,95 @@
       <c r="AJ90" s="10" t="n"/>
       <c r="AK90" s="11" t="n"/>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
+    <row r="91" ht="234" customHeight="1">
+      <c r="C91" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "shiten_id": 5,
+  "ja_id": 1,
+  "shiten_code": "S05",
+  "shiten_name": "削除対象支店",
+  "shiten_name_kana": "サクジョタイショウシテン",
+  "kinyu_shiten_flg": false,
+  "kanri_shiten_id": 1,
+  "biko": "テスト用支店"
+}</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="10" t="n"/>
+      <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="11" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
         <is>
           <t>成功メッセージを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="B93" s="27" t="inlineStr">
+    <row r="94" ht="18" customHeight="1">
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>4.8 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="C95" s="41" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="216" customHeight="1">
-      <c r="C96" s="42" t="inlineStr">
+    <row r="97" ht="216" customHeight="1">
+      <c r="C97" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -8756,43 +9175,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n"/>
-      <c r="E96" s="10" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="10" t="n"/>
-      <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
-      <c r="J96" s="10" t="n"/>
-      <c r="K96" s="10" t="n"/>
-      <c r="L96" s="10" t="n"/>
-      <c r="M96" s="10" t="n"/>
-      <c r="N96" s="10" t="n"/>
-      <c r="O96" s="10" t="n"/>
-      <c r="P96" s="10" t="n"/>
-      <c r="Q96" s="10" t="n"/>
-      <c r="R96" s="10" t="n"/>
-      <c r="S96" s="10" t="n"/>
-      <c r="T96" s="10" t="n"/>
-      <c r="U96" s="10" t="n"/>
-      <c r="V96" s="10" t="n"/>
-      <c r="W96" s="10" t="n"/>
-      <c r="X96" s="10" t="n"/>
-      <c r="Y96" s="10" t="n"/>
-      <c r="Z96" s="10" t="n"/>
-      <c r="AA96" s="10" t="n"/>
-      <c r="AB96" s="10" t="n"/>
-      <c r="AC96" s="10" t="n"/>
-      <c r="AD96" s="10" t="n"/>
-      <c r="AE96" s="10" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
-      <c r="AI96" s="10" t="n"/>
-      <c r="AJ96" s="10" t="n"/>
-      <c r="AK96" s="11" t="n"/>
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="10" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
+      <c r="U97" s="10" t="n"/>
+      <c r="V97" s="10" t="n"/>
+      <c r="W97" s="10" t="n"/>
+      <c r="X97" s="10" t="n"/>
+      <c r="Y97" s="10" t="n"/>
+      <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="10" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="10" t="n"/>
+      <c r="AK97" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="127">
+  <mergeCells count="128">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="C57:AK57"/>
@@ -8807,9 +9226,7 @@
     <mergeCell ref="D64:AK64"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D82:AK82"/>
     <mergeCell ref="C45:AK45"/>
-    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
@@ -8818,8 +9235,6 @@
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="C65:AK65"/>
-    <mergeCell ref="C94:AK94"/>
-    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
@@ -8832,11 +9247,9 @@
     <mergeCell ref="D77:AK77"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="C48:AK48"/>
-    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="D75:AK75"/>
     <mergeCell ref="T30:X30"/>
-    <mergeCell ref="B93:AK93"/>
     <mergeCell ref="B47:I47"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="Z1:AC1"/>
@@ -8846,8 +9259,6 @@
     <mergeCell ref="C33:AK33"/>
     <mergeCell ref="B61:AK61"/>
     <mergeCell ref="C42:AK42"/>
-    <mergeCell ref="C88:AK88"/>
-    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
@@ -8858,6 +9269,7 @@
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
@@ -8871,25 +9283,31 @@
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="C96:AK96"/>
+    <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C54:AK54"/>
     <mergeCell ref="C63:AK63"/>
+    <mergeCell ref="B84:AK84"/>
+    <mergeCell ref="C93:AK93"/>
+    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="A60:AK60"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="B94:AK94"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="C36:AK36"/>
     <mergeCell ref="V2:Y3"/>
@@ -8902,14 +9320,15 @@
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="C69:AK69"/>
-    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="A22:AK22"/>
     <mergeCell ref="D74:AK74"/>
+    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
+    <mergeCell ref="B88:AK88"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B53:I53"/>
-    <mergeCell ref="B83:AK83"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
@@ -8919,6 +9338,7 @@
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="B62:AK62"/>
     <mergeCell ref="D70:AK70"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
